--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>88.02239860575715</v>
+        <v>14.30363977343554</v>
       </c>
       <c r="D2" t="n">
-        <v>88.02762964082368</v>
+        <v>14.30448981663385</v>
       </c>
       <c r="E2" t="n">
-        <v>18.83672283921645</v>
+        <v>3.060967461372674</v>
       </c>
       <c r="F2" t="n">
-        <v>18.81161799535358</v>
+        <v>3.056887924244957</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.0418139801039</v>
+        <v>11.86929477176688</v>
       </c>
       <c r="D3" t="n">
-        <v>73.07976119939092</v>
+        <v>11.87546119490102</v>
       </c>
       <c r="E3" t="n">
-        <v>18.83672283921645</v>
+        <v>3.060967461372674</v>
       </c>
       <c r="F3" t="n">
-        <v>18.81161799535358</v>
+        <v>3.056887924244957</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.0386138784657</v>
+        <v>8.943774755250676</v>
       </c>
       <c r="D4" t="n">
-        <v>55.01211197566148</v>
+        <v>8.939468196044992</v>
       </c>
       <c r="E4" t="n">
-        <v>18.83672283921645</v>
+        <v>3.060967461372674</v>
       </c>
       <c r="F4" t="n">
-        <v>18.81161799535358</v>
+        <v>3.056887924244957</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.90118731649445</v>
+        <v>6.158942938930348</v>
       </c>
       <c r="D5" t="n">
-        <v>38.0031185854822</v>
+        <v>6.175506770140857</v>
       </c>
       <c r="E5" t="n">
-        <v>18.83672283921645</v>
+        <v>3.060967461372674</v>
       </c>
       <c r="F5" t="n">
-        <v>18.81161799535358</v>
+        <v>3.056887924244957</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
